--- a/results/Int Task Remove ACC -0.3/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_2_permute.xlsx
@@ -440,557 +440,557 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7120710498835248</v>
+        <v>0.7255052614667845</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7113930837818299</v>
+        <v>0.7203777411840309</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7023656518595871</v>
+        <v>0.7319031649128445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7302146758775805</v>
+        <v>0.7267392963290225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7296222588159691</v>
+        <v>0.7246989718049642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7296222588159691</v>
+        <v>0.7246989718049642</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7317449192706241</v>
+        <v>0.7248240822556029</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7369547754839747</v>
+        <v>0.7487272070045787</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7367441159932524</v>
+        <v>0.7539798377379709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7249716844726484</v>
+        <v>0.7767473291027391</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.724379267411037</v>
+        <v>0.776921640292393</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7275947867298578</v>
+        <v>0.762611655554663</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7259426459956624</v>
+        <v>0.7634970680375934</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7233227568479397</v>
+        <v>0.7635826170776769</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6988400674752993</v>
+        <v>0.7646092055586795</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6720465499236887</v>
+        <v>0.7646092055586795</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6538035183548879</v>
+        <v>0.7519118001445899</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6476461964816451</v>
+        <v>0.75119427263234</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6473499879508394</v>
+        <v>0.7338035183548879</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.620474134468632</v>
+        <v>0.7311707767692184</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6271383243634027</v>
+        <v>0.7204516427022252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6248969796770825</v>
+        <v>0.714853602699012</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6276281227407824</v>
+        <v>0.7240981203309502</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6216216161940717</v>
+        <v>0.7247365250220901</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6051098481805768</v>
+        <v>0.7038340428950116</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6135213671780866</v>
+        <v>0.7038340428950116</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6272485741826653</v>
+        <v>0.7002271266768415</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6420087958872198</v>
+        <v>0.6513099445738613</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6429829705197204</v>
+        <v>0.6342645995662302</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6347949634508796</v>
+        <v>0.6328658928427986</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6318959354164992</v>
+        <v>0.5966214153747289</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6274955819744558</v>
+        <v>0.5746196481645112</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6162727929954213</v>
+        <v>0.5895519720459474</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.59979636918628</v>
+        <v>0.5912041127801431</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5915838621576031</v>
+        <v>0.5916414973090208</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6074369427263234</v>
+        <v>0.5969433287814282</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6005022491766407</v>
+        <v>0.6023702707044742</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6038396658366134</v>
+        <v>0.583756124989959</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6070583982649209</v>
+        <v>0.5774897582135111</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6070583982649209</v>
+        <v>0.5831369989557394</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.616879267411037</v>
+        <v>0.6540882801831472</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5544282673307093</v>
+        <v>0.6076658767772511</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5544282673307093</v>
+        <v>0.5777616676038236</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5627626717005383</v>
+        <v>0.5692443168125955</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5758836051088441</v>
+        <v>0.5709392320668327</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5758836051088441</v>
+        <v>0.5686679652984176</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.570663105470319</v>
+        <v>0.5703928026347498</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5520640212065226</v>
+        <v>0.5703928026347498</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5530381958390232</v>
+        <v>0.5517615872760864</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5527419873082176</v>
+        <v>0.55184713631617</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4838589444935336</v>
+        <v>0.5504879910032934</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4760334163386617</v>
+        <v>0.5521433448469757</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4262211824242911</v>
+        <v>0.5242334725680777</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4045626154711222</v>
+        <v>0.5217750421720619</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3720993654108764</v>
+        <v>0.5217750421720619</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3646021768816772</v>
+        <v>0.5219857016627841</v>
       </c>
     </row>
     <row r="58">
@@ -1000,327 +1000,327 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3635852277291349</v>
+        <v>0.5219857016627841</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3726094465418909</v>
+        <v>0.5156337858462527</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3693607920314885</v>
+        <v>0.4999347337135513</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3707456422202586</v>
+        <v>0.500826572415455</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.3697843200257049</v>
+        <v>0.5029588721985702</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.3753855731384047</v>
+        <v>0.5029588721985702</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3950230942244357</v>
+        <v>0.5000823359305968</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.3952765282351996</v>
+        <v>0.5016061531046671</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4775714916860792</v>
+        <v>0.4973244838942887</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4851574423648486</v>
+        <v>0.497877339545345</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4817151980078721</v>
+        <v>0.4998256888103462</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4882446381235441</v>
+        <v>0.4998256888103462</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4882446381235441</v>
+        <v>0.4990621736685678</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.488498072134308</v>
+        <v>0.4989370632179291</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4801058317937184</v>
+        <v>0.4983446461563178</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4754851795324926</v>
+        <v>0.4983446461563178</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4752349586312153</v>
+        <v>0.4957183307896216</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4775650654671058</v>
+        <v>0.492914491123785</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4901994136075187</v>
+        <v>0.4964754197124267</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.496857177283316</v>
+        <v>0.495330146999759</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.496857177283316</v>
+        <v>0.4948232789782312</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4961727849626476</v>
+        <v>0.4965117680134951</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5067935175516106</v>
+        <v>0.4955311671620211</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5107693389027231</v>
+        <v>0.4958701502128685</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.510173708731625</v>
+        <v>0.4971501727046349</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5142318660133344</v>
+        <v>0.4888798297051972</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5148670575949875</v>
+        <v>0.4878201060326131</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5135934613221945</v>
+        <v>0.4911340268294642</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5131325809301952</v>
+        <v>0.4928620772752831</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5148670575949875</v>
+        <v>0.4979960237770102</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5134715639810427</v>
+        <v>0.4992792593782633</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5058438428789461</v>
+        <v>0.496988713952928</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5007131094867058</v>
+        <v>0.4992792593782633</v>
       </c>
     </row>
   </sheetData>
